--- a/marketing_forms/006_snack_brand_collaboration_registration_form--marketing_forms.xlsx
+++ b/marketing_forms/006_snack_brand_collaboration_registration_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_info</t>
+          <t>submission_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>User Info</t>
+          <t>Submission Info</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>snack_brand_info</t>
+          <t>submission_info_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Snack Brand Info</t>
+          <t>More Submission Info</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>collaboration_info</t>
+          <t>submission_status_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Collaboration Info</t>
+          <t>Follow up question</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submission_info</t>
+          <t>submission_status_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Submission Info</t>
+          <t>Another follow up question</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_inputs_2</t>
+          <t>submission_info_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>User Inputs 2</t>
+          <t>More details about the submission</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>submission_status_2</t>
+          <t>submission_status_3_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Submission Status 2</t>
+          <t>Submission Status 3 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>collaboration_requests_2</t>
+          <t>submission_info_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Collaboration Requests 2</t>
+          <t>Even more details about the submission</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submission_info_2</t>
+          <t>submission_status_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Submission Info 2</t>
+          <t>Last follow up question</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>collaboration_requests</t>
+          <t>submission_info_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Collaboration Requests</t>
+          <t>Additional information about the submission</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submission_status</t>
+          <t>submission_status_5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submission Status</t>
+          <t>Final follow up question</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submission_info</t>
+          <t>submission_info_6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submission Info</t>
+          <t>Last additional comments or information</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,660 +865,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>user_inputs_3</t>
+          <t>submission_status_6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>User Inputs 3</t>
+          <t>Final submission status</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submission_status_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Submission Status 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>collaboration_requests_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Collaboration Requests 2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submission_info_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submission Info 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>collaboration_requests_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Collaboration Requests 3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submission_status_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submission Status 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submission_info_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Submission Info 3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submission_status_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submission Status 4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>submission_info_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Submission Info 4</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission_info_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission Info 5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>submission_status_5</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Submission Status 5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>submission_info_6</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Submission Info 6</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>submission_status_6</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Submission Status 6</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>submission_info_7</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Submission Info 7</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>submission_status_7</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Submission Status 7</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>submission_info_8</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Submission Info 8</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>submission_status_8</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Submission Status 8</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>submission_info_9</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Submission Info 9</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>submission_status_9</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Submission Status 9</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>submission_info_10</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Submission Info 10</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>submission_status_10</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Submission Status 10</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>submission_info_11</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Submission Info 11</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>submission_status_11</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Submission Status 11</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>submission_info_12</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Submission Info 12</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>submission_status_12</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Submission Status 12</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>submission_info_13</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Submission Info 13</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>submission_status_13</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Submission Status 13</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>submission_info_14</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Submission Info 14</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>submission_status_14</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Submission Status 14</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1539,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1568,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1585,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1602,29 +958,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>collaboration_requests_choices</t>
+          <t>submission_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1636,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
